--- a/StructureDefinition-SEEHDSLMLaboratoryOrderOutcomeV41.xlsx
+++ b/StructureDefinition-SEEHDSLMLaboratoryOrderOutcomeV41.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMLaboratoryOrderOutcomeV41.xlsx
+++ b/StructureDefinition-SEEHDSLMLaboratoryOrderOutcomeV41.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6041" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6041" uniqueCount="484">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1203,6 +1203,10 @@
     <t>Angivelse av utfall av en utförd analys angiven med en och endast en av datatyperna: Physical Quantity (PQ) I PQ.value anges ett numeriskt värde I PQ.unit anges en måttenhet enligt referens [R10]. Intervall av Physical Quantity IVL&lt;PQ&gt; IVL&lt;PQ&gt;.low Det numeriska värdet som utgör den lägre delen av intervallet IVL&lt;PQ&gt;.lowClosed Angivelse av om värdet är en del av intervallet eller ej. Exempel: lowClosed = true och low = 5 motsvarar intervallet ≥ 5 lowClosed = false och low = 5 motsvarar intervallet &gt; 5 IVL&lt;PQ&gt;.high Det numeriska värdet som utgör den högre delen av intervallet IVL&lt;PQ&gt;.highClosed Exempel: highClosed = true och high = 10 motsvarar intervallet ≤ 10 highClosed = false och high = 10 motsvarar intervallet &lt; 10 Sträng ST Textuellt resultat Kodat värde CV Kodat värde</t>
   </si>
   <si>
+    <t>getlaboratoryorderoutcome-value-choice:En och endast en av cv, pq, intervalPQ och st ska anges {cv.combine(pq).combine(intervalPQ).combine(st).count() = 1}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+  </si>
+  <si>
     <t>SEEHDSLMLaboratoryOrderOutcomeV41.laboratoryOrderOutcome.body.groupOfAnalyses.analysis.result.value.id</t>
   </si>
   <si>
@@ -1269,6 +1273,10 @@
   </si>
   <si>
     <t>Information om vilket referensintervall eller referensvärde som gäller för ett resultat.</t>
+  </si>
+  <si>
+    <t>getlaboratoryorderoutcome-reference-choice:Ett och endast ett av interval och description ska anges {interval.exists() xor description.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>SEEHDSLMLaboratoryOrderOutcomeV41.laboratoryOrderOutcome.body.groupOfAnalyses.analysis.result.reference.id</t>
@@ -15752,15 +15760,15 @@
         <v>72</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>81</v>
+        <v>387</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15857,10 +15865,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -15959,10 +15967,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16063,10 +16071,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16092,10 +16100,10 @@
         <v>177</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -16146,7 +16154,7 @@
         <v>72</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>73</v>
@@ -16163,10 +16171,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16189,13 +16197,13 @@
         <v>72</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -16246,7 +16254,7 @@
         <v>72</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>73</v>
@@ -16263,10 +16271,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16289,13 +16297,13 @@
         <v>72</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -16346,7 +16354,7 @@
         <v>72</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>73</v>
@@ -16363,10 +16371,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16392,10 +16400,10 @@
         <v>129</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -16446,7 +16454,7 @@
         <v>72</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>73</v>
@@ -16463,10 +16471,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16492,10 +16500,10 @@
         <v>129</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -16546,7 +16554,7 @@
         <v>72</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>73</v>
@@ -16563,10 +16571,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -16592,10 +16600,10 @@
         <v>177</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -16646,7 +16654,7 @@
         <v>72</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>73</v>
@@ -16663,10 +16671,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16692,10 +16700,10 @@
         <v>78</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -16746,7 +16754,7 @@
         <v>72</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>73</v>
@@ -16758,15 +16766,15 @@
         <v>72</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>81</v>
+        <v>410</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -16863,10 +16871,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -16965,10 +16973,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17069,10 +17077,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17095,13 +17103,13 @@
         <v>72</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -17152,7 +17160,7 @@
         <v>72</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>73</v>
@@ -17169,10 +17177,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17198,10 +17206,10 @@
         <v>129</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -17252,7 +17260,7 @@
         <v>72</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>73</v>
@@ -17269,10 +17277,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17298,10 +17306,10 @@
         <v>129</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -17352,7 +17360,7 @@
         <v>72</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>73</v>
@@ -17369,10 +17377,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17398,10 +17406,10 @@
         <v>129</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -17452,7 +17460,7 @@
         <v>72</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>73</v>
@@ -17469,10 +17477,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17498,10 +17506,10 @@
         <v>78</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -17552,7 +17560,7 @@
         <v>72</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>73</v>
@@ -17569,10 +17577,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17669,10 +17677,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17771,10 +17779,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -17875,10 +17883,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -17904,10 +17912,10 @@
         <v>119</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -17958,7 +17966,7 @@
         <v>72</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>73</v>
@@ -17975,10 +17983,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18007,7 +18015,7 @@
         <v>171</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -18058,7 +18066,7 @@
         <v>72</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>73</v>
@@ -18075,10 +18083,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18104,10 +18112,10 @@
         <v>133</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -18158,7 +18166,7 @@
         <v>72</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>83</v>
@@ -18175,10 +18183,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18258,7 +18266,7 @@
         <v>72</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>73</v>
@@ -18275,10 +18283,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18304,10 +18312,10 @@
         <v>78</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -18358,7 +18366,7 @@
         <v>72</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>73</v>
@@ -18375,10 +18383,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18475,10 +18483,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18577,10 +18585,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18681,10 +18689,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -18710,10 +18718,10 @@
         <v>119</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -18764,7 +18772,7 @@
         <v>72</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>73</v>
@@ -18781,10 +18789,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -18813,7 +18821,7 @@
         <v>171</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -18864,7 +18872,7 @@
         <v>72</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>73</v>
@@ -18881,10 +18889,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -18910,10 +18918,10 @@
         <v>133</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -18964,7 +18972,7 @@
         <v>72</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>83</v>
@@ -18981,10 +18989,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19064,7 +19072,7 @@
         <v>72</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>73</v>
@@ -19081,10 +19089,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19110,10 +19118,10 @@
         <v>72</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -19164,7 +19172,7 @@
         <v>72</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>73</v>
@@ -19181,10 +19189,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19210,10 +19218,10 @@
         <v>78</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -19264,7 +19272,7 @@
         <v>72</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>83</v>
@@ -19281,10 +19289,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19381,10 +19389,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -19483,10 +19491,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -19587,10 +19595,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -19616,10 +19624,10 @@
         <v>119</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
@@ -19670,7 +19678,7 @@
         <v>72</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>73</v>
@@ -19687,10 +19695,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -19716,10 +19724,10 @@
         <v>129</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
@@ -19770,7 +19778,7 @@
         <v>72</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>83</v>
@@ -19787,10 +19795,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -19819,7 +19827,7 @@
         <v>193</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -19870,7 +19878,7 @@
         <v>72</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>73</v>
@@ -19887,10 +19895,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -19987,10 +19995,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -20089,10 +20097,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -20193,10 +20201,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -20222,10 +20230,10 @@
         <v>119</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -20276,7 +20284,7 @@
         <v>72</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>73</v>
@@ -20293,10 +20301,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -20376,7 +20384,7 @@
         <v>72</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>73</v>
@@ -20393,10 +20401,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -20422,10 +20430,10 @@
         <v>133</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
@@ -20476,7 +20484,7 @@
         <v>72</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>83</v>
@@ -20493,10 +20501,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -20576,7 +20584,7 @@
         <v>72</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>73</v>
@@ -20593,10 +20601,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -20622,10 +20630,10 @@
         <v>78</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
@@ -20676,7 +20684,7 @@
         <v>72</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>73</v>
@@ -20693,10 +20701,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -20793,10 +20801,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -20895,10 +20903,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -20999,10 +21007,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21028,10 +21036,10 @@
         <v>129</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
@@ -21082,7 +21090,7 @@
         <v>72</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>83</v>

--- a/StructureDefinition-SEEHDSLMLaboratoryOrderOutcomeV41.xlsx
+++ b/StructureDefinition-SEEHDSLMLaboratoryOrderOutcomeV41.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMLaboratoryOrderOutcomeV41.xlsx
+++ b/StructureDefinition-SEEHDSLMLaboratoryOrderOutcomeV41.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
